--- a/public/data/companies.xlsx
+++ b/public/data/companies.xlsx
@@ -433,13 +433,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>59d80d33-537e-4a37-8655-1739660ec5d4</v>
+        <v>3878f7f2-c5c5-48c0-9178-4fed0b5ffef5</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>Marriott International</v>
@@ -465,13 +465,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>13d45613-2988-4ea6-80b8-5f95f812cfb4</v>
+        <v>777dac53-12bf-48ef-a913-ac3e14639321</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
         <v>Soneva Group</v>
@@ -497,13 +497,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>49848a44-2a6a-4193-8607-c2ca1897d7a7</v>
+        <v>2d720ce4-b7e5-4a56-bebe-46ba7ddefe65</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
         <v>LVMH Hospitality</v>
@@ -529,13 +529,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>fa50e21f-d5b2-4543-8b76-17007d80b959</v>
+        <v>b90a2822-5146-4bc6-8193-1413cd5a2e04</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
         <v>Four Seasons Hotels &amp; Resorts</v>
@@ -561,13 +561,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>e9ce8fb9-566a-4b6e-88e6-012467e48a71</v>
+        <v>00814f5b-b883-4ca7-b853-b2667ab37505</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
         <v>Minor International (Anantara)</v>
@@ -593,13 +593,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>99492203-f941-48e8-923d-076e492f5230</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
         <v>Soneva Fushi</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>53bca1fc-519c-458e-91f3-f73ab9c834fe</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
         <v>Waldorf Astoria Maldives Ithaafushi</v>
@@ -657,13 +657,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>819129ff-9f49-45d0-92b3-d595220fdfb5</v>
+        <v>42e6bcee-426a-4f7a-877e-20c9962142d5</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
         <v>St. Regis Maldives Vommuli</v>
@@ -689,13 +689,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>44e8275f-6dbf-4a68-8aa8-3a6a09ecac5e</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
         <v>Patina Maldives Fari Islands</v>
@@ -721,13 +721,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ae61d497-ed25-4ed3-b6f5-07f017123cbd</v>
+        <v>c4b758b0-8279-41c1-9617-c33355bf329a</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
         <v>Cheval Blanc Randheli</v>
@@ -753,13 +753,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>c4b72dfb-694a-4cd6-a5be-cb1bddcaa2a5</v>
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D12" t="str">
         <v>Four Seasons Landaa Giraavaru</v>
@@ -785,13 +785,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>9fda538c-f70f-447b-9d9a-f641700abf98</v>
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D13" t="str">
         <v>Four Seasons Kuda Huraa</v>
@@ -817,13 +817,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>79958ed2-9c5b-421b-98f3-26062254d840</v>
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D14" t="str">
         <v>Anantara Kihavah Maldives</v>
@@ -849,13 +849,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>28f29363-bd63-4176-95b1-4de2fd79edf4</v>
+        <v>7a7a2625-26bd-424d-acbe-9c84fc54ea85</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D15" t="str">
         <v>The Ritz-Carlton Maldives Fari Islands</v>
@@ -881,13 +881,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>b2c6555b-31b8-470c-a25d-e7b05dadb044</v>
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D16" t="str">
         <v>Soneva Jani</v>
